--- a/public/uploads/users.xlsx
+++ b/public/uploads/users.xlsx
@@ -15,87 +15,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3">
   <si>
     <t>EMP ID</t>
   </si>
   <si>
-    <t>First Name</t>
+    <t>Employee Name</t>
   </si>
   <si>
-    <t>Last Name</t>
-  </si>
-  <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Over Time</t>
-  </si>
-  <si>
-    <t>Gross Wages</t>
-  </si>
-  <si>
-    <t>Deduction</t>
-  </si>
-  <si>
-    <t>Payroll</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>Rahul</t>
-  </si>
-  <si>
-    <t>Singh</t>
-  </si>
-  <si>
-    <t>fgbf475</t>
-  </si>
-  <si>
-    <t>Amazing</t>
-  </si>
-  <si>
-    <t>Tech</t>
-  </si>
-  <si>
-    <t>ABC &amp; Company Ltd.</t>
-  </si>
-  <si>
-    <t>Guru Gram</t>
-  </si>
-  <si>
-    <t>singh</t>
-  </si>
-  <si>
-    <t>ldfj</t>
-  </si>
-  <si>
-    <t>Shani</t>
-  </si>
-  <si>
-    <t>sharma</t>
-  </si>
-  <si>
-    <t>Deeksha</t>
-  </si>
-  <si>
-    <t>rfg</t>
-  </si>
-  <si>
-    <t>frg</t>
-  </si>
-  <si>
-    <t>test200</t>
-  </si>
-  <si>
-    <t>Sharma</t>
-  </si>
-  <si>
-    <t>Vipan</t>
+    <t>User</t>
   </si>
 </sst>
 </file>
@@ -435,245 +363,23 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:2">
       <c r="A2">
-        <v>73587458</v>
+        <v>12245</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3">
-        <v>51626266</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5">
-        <v>1717331145</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6">
-        <v>8055987</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7">
-        <v>5412289</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8">
-        <v>5859013</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9">
-        <v>7445776</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10">
-        <v>4596373</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11">
-        <v>2842458</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/public/uploads/users.xlsx
+++ b/public/uploads/users.xlsx
@@ -15,15 +15,195 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3">
-  <si>
-    <t>EMP ID</t>
-  </si>
-  <si>
-    <t>Employee Name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Middle Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Secondory Email</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Alternate Mobile</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Date of Birth</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Local Address Line 1</t>
+  </si>
+  <si>
+    <t>Local Address Line 2</t>
+  </si>
+  <si>
+    <t>Local City/Town</t>
+  </si>
+  <si>
+    <t>Local Country</t>
+  </si>
+  <si>
+    <t>Local State</t>
+  </si>
+  <si>
+    <t>Local Post Code</t>
+  </si>
+  <si>
+    <t>Permanent Address Line 1</t>
+  </si>
+  <si>
+    <t>Permanent Address Line 2</t>
+  </si>
+  <si>
+    <t>Permanent City/Town</t>
+  </si>
+  <si>
+    <t>Permanent Country</t>
+  </si>
+  <si>
+    <t>Permanent State</t>
+  </si>
+  <si>
+    <t>Permanent Post Code</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>Date of joining</t>
+  </si>
+  <si>
+    <t>Probation End Date</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Qualification Degree</t>
+  </si>
+  <si>
+    <t>Work Experience</t>
+  </si>
+  <si>
+    <t>Immediate Manager</t>
+  </si>
+  <si>
+    <t>Immediate Manager Employee Code</t>
+  </si>
+  <si>
+    <t>Leave Approving Authority</t>
+  </si>
+  <si>
+    <t>Leave Approving Authority Employee Code</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Job Role</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>Employement Type</t>
+  </si>
+  <si>
+    <t>Aadhar Number</t>
+  </si>
+  <si>
+    <t>PAN Number</t>
+  </si>
+  <si>
+    <t>Holiday Year</t>
+  </si>
+  <si>
+    <t>Work Pattern</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Annual Earned Leave Entilement</t>
+  </si>
+  <si>
+    <t>This Year</t>
+  </si>
+  <si>
+    <t>Next Year</t>
+  </si>
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>Middle</t>
+  </si>
+  <si>
+    <t>Last</t>
+  </si>
+  <si>
+    <t>user@gmail.com</t>
+  </si>
+  <si>
+    <t>user1@gmail.com</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>1995-07-10</t>
+  </si>
+  <si>
+    <t>Address 1</t>
+  </si>
+  <si>
+    <t>Address 2</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
+    <t>2024-02-01</t>
   </si>
   <si>
     <t>User</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>2024-2025</t>
+  </si>
+  <si>
+    <t>Full Time</t>
   </si>
 </sst>
 </file>
@@ -363,23 +543,251 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>12245</v>
+    <row r="2" spans="1:45">
+      <c r="A2" t="s">
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2">
+        <v>1234567894</v>
+      </c>
+      <c r="G2">
+        <v>7894561235</v>
+      </c>
+      <c r="H2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2">
+        <v>123456</v>
+      </c>
+      <c r="K2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2">
+        <v>123456</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" t="s">
+        <v>53</v>
+      </c>
+      <c r="S2" t="s">
+        <v>54</v>
+      </c>
+      <c r="T2" t="s">
+        <v>55</v>
+      </c>
+      <c r="U2" t="s">
+        <v>56</v>
+      </c>
+      <c r="V2">
+        <v>123456</v>
+      </c>
+      <c r="W2">
+        <v>908025</v>
+      </c>
+      <c r="X2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/public/uploads/users.xlsx
+++ b/public/uploads/users.xlsx
@@ -20,190 +20,190 @@
     <t>First Name</t>
   </si>
   <si>
-    <t>Middle Name</t>
-  </si>
-  <si>
-    <t>Last Name</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Secondory Email</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>Alternate Mobile</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>Date of Birth</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Local Address Line 1</t>
-  </si>
-  <si>
-    <t>Local Address Line 2</t>
-  </si>
-  <si>
-    <t>Local City/Town</t>
-  </si>
-  <si>
-    <t>Local Country</t>
-  </si>
-  <si>
-    <t>Local State</t>
-  </si>
-  <si>
-    <t>Local Post Code</t>
-  </si>
-  <si>
-    <t>Permanent Address Line 1</t>
-  </si>
-  <si>
-    <t>Permanent Address Line 2</t>
-  </si>
-  <si>
-    <t>Permanent City/Town</t>
-  </si>
-  <si>
-    <t>Permanent Country</t>
-  </si>
-  <si>
-    <t>Permanent State</t>
-  </si>
-  <si>
-    <t>Permanent Post Code</t>
-  </si>
-  <si>
-    <t>Employee ID</t>
-  </si>
-  <si>
-    <t>Date of joining</t>
-  </si>
-  <si>
-    <t>Probation End Date</t>
-  </si>
-  <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Qualification Degree</t>
-  </si>
-  <si>
-    <t>Work Experience</t>
-  </si>
-  <si>
-    <t>Immediate Manager</t>
-  </si>
-  <si>
-    <t>Immediate Manager Employee Code</t>
-  </si>
-  <si>
-    <t>Leave Approving Authority</t>
-  </si>
-  <si>
-    <t>Leave Approving Authority Employee Code</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Job Role</t>
-  </si>
-  <si>
-    <t>Grade</t>
-  </si>
-  <si>
-    <t>Employement Type</t>
-  </si>
-  <si>
-    <t>Aadhar Number</t>
-  </si>
-  <si>
-    <t>PAN Number</t>
-  </si>
-  <si>
-    <t>Holiday Year</t>
-  </si>
-  <si>
-    <t>Work Pattern</t>
-  </si>
-  <si>
-    <t>Salary</t>
-  </si>
-  <si>
-    <t>Annual Earned Leave Entilement</t>
-  </si>
-  <si>
-    <t>This Year</t>
-  </si>
-  <si>
-    <t>Next Year</t>
+    <t>last Name</t>
+  </si>
+  <si>
+    <t>Rishi</t>
+  </si>
+  <si>
+    <t>Shukla</t>
+  </si>
+  <si>
+    <t>Web</t>
+  </si>
+  <si>
+    <t>oum</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Singh</t>
+  </si>
+  <si>
+    <t>Ayush</t>
+  </si>
+  <si>
+    <t>mishra</t>
+  </si>
+  <si>
+    <t>Suraj</t>
+  </si>
+  <si>
+    <t>HR web</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>Shubham</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>Shubh</t>
+  </si>
+  <si>
+    <t>S123</t>
+  </si>
+  <si>
+    <t>Sourav</t>
+  </si>
+  <si>
+    <t>Thakur</t>
+  </si>
+  <si>
+    <t>Kuldeep</t>
+  </si>
+  <si>
+    <t>Chahal</t>
+  </si>
+  <si>
+    <t>Nikhil</t>
+  </si>
+  <si>
+    <t>Saini</t>
+  </si>
+  <si>
+    <t>Rohit</t>
+  </si>
+  <si>
+    <t>Deshmukh</t>
+  </si>
+  <si>
+    <t>Karan</t>
+  </si>
+  <si>
+    <t>Rawat</t>
+  </si>
+  <si>
+    <t>Ajay</t>
+  </si>
+  <si>
+    <t>Atul</t>
+  </si>
+  <si>
+    <t>Abdul</t>
+  </si>
+  <si>
+    <t>Tkhan</t>
+  </si>
+  <si>
+    <t>Sunil</t>
+  </si>
+  <si>
+    <t>Kumar</t>
+  </si>
+  <si>
+    <t>yadav</t>
+  </si>
+  <si>
+    <t>Nayan</t>
+  </si>
+  <si>
+    <t>Ganguly</t>
+  </si>
+  <si>
+    <t>Banerjee</t>
+  </si>
+  <si>
+    <t>Amit</t>
+  </si>
+  <si>
+    <t>Rachin</t>
+  </si>
+  <si>
+    <t>Ahmed</t>
+  </si>
+  <si>
+    <t>vaibhav</t>
+  </si>
+  <si>
+    <t>kumar</t>
+  </si>
+  <si>
+    <t>testleave</t>
+  </si>
+  <si>
+    <t>shubham</t>
+  </si>
+  <si>
+    <t>test emp</t>
+  </si>
+  <si>
+    <t>test emp last</t>
+  </si>
+  <si>
+    <t>onboard</t>
+  </si>
+  <si>
+    <t>onboar last</t>
+  </si>
+  <si>
+    <t>Retest</t>
+  </si>
+  <si>
+    <t>User151</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>usernew</t>
+  </si>
+  <si>
+    <t>devansh</t>
+  </si>
+  <si>
+    <t>Ranjeet</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>Test Import</t>
+  </si>
+  <si>
+    <t>Last</t>
   </si>
   <si>
     <t>First</t>
   </si>
   <si>
-    <t>Middle</t>
-  </si>
-  <si>
-    <t>Last</t>
-  </si>
-  <si>
-    <t>user@gmail.com</t>
-  </si>
-  <si>
-    <t>user1@gmail.com</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>1995-07-10</t>
-  </si>
-  <si>
-    <t>Address 1</t>
-  </si>
-  <si>
-    <t>Address 2</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
-    <t>2024-02-01</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>Regular</t>
-  </si>
-  <si>
-    <t>2024-2025</t>
-  </si>
-  <si>
-    <t>Full Time</t>
+    <t>Vipan</t>
+  </si>
+  <si>
+    <t>Arsh</t>
+  </si>
+  <si>
+    <t>Mehta</t>
+  </si>
+  <si>
+    <t>Aditya</t>
   </si>
 </sst>
 </file>
@@ -543,251 +543,367 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AS2"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:45">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="B11" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="B12" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="B13" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="B14" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="B15" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="B18" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="B19" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="B21" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="B24" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="B25" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="B26">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:45">
-      <c r="A2" t="s">
+      <c r="B29" t="s">
         <v>45</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
         <v>46</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B30" t="s">
         <v>47</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
         <v>48</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B31" t="s">
         <v>49</v>
       </c>
-      <c r="F2">
-        <v>1234567894</v>
-      </c>
-      <c r="G2">
-        <v>7894561235</v>
-      </c>
-      <c r="H2" t="s">
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
         <v>50</v>
       </c>
-      <c r="I2" t="s">
+      <c r="B32" t="s">
         <v>51</v>
       </c>
-      <c r="J2">
-        <v>123456</v>
-      </c>
-      <c r="K2" t="s">
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
         <v>52</v>
       </c>
-      <c r="L2" t="s">
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
         <v>53</v>
       </c>
-      <c r="M2" t="s">
+      <c r="B36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
         <v>54</v>
       </c>
-      <c r="N2" t="s">
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" t="s">
         <v>55</v>
       </c>
-      <c r="O2" t="s">
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
         <v>56</v>
       </c>
-      <c r="P2">
-        <v>123456</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R2" t="s">
-        <v>53</v>
-      </c>
-      <c r="S2" t="s">
-        <v>54</v>
-      </c>
-      <c r="T2" t="s">
-        <v>55</v>
-      </c>
-      <c r="U2" t="s">
-        <v>56</v>
-      </c>
-      <c r="V2">
-        <v>123456</v>
-      </c>
-      <c r="W2">
-        <v>908025</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="B40" t="s">
         <v>57</v>
       </c>
-      <c r="Y2" t="s">
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
         <v>58</v>
       </c>
-      <c r="Z2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI2" t="s">
+      <c r="B41" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
         <v>59</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
         <v>60</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="B43" t="s">
         <v>61</v>
       </c>
-      <c r="AO2" t="s">
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
         <v>62</v>
       </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/public/uploads/users.xlsx
+++ b/public/uploads/users.xlsx
@@ -15,21 +15,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="147">
   <si>
     <t>First Name</t>
   </si>
   <si>
-    <t>Middle Name</t>
-  </si>
-  <si>
-    <t>Last Name</t>
+    <t>last Name</t>
   </si>
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>Secondory Email</t>
+    <t>Secondary Email</t>
   </si>
   <si>
     <t>Mobile</t>
@@ -44,163 +41,421 @@
     <t>Date of Birth</t>
   </si>
   <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Local Address Line 1</t>
-  </si>
-  <si>
-    <t>Local Address Line 2</t>
-  </si>
-  <si>
-    <t>Local City/Town</t>
-  </si>
-  <si>
-    <t>Local Country</t>
-  </si>
-  <si>
-    <t>Local State</t>
-  </si>
-  <si>
-    <t>Local Post Code</t>
-  </si>
-  <si>
-    <t>Permanent Address Line 1</t>
-  </si>
-  <si>
-    <t>Permanent Address Line 2</t>
-  </si>
-  <si>
-    <t>Permanent City/Town</t>
-  </si>
-  <si>
-    <t>Permanent Country</t>
-  </si>
-  <si>
-    <t>Permanent State</t>
-  </si>
-  <si>
-    <t>Permanent Post Code</t>
-  </si>
-  <si>
-    <t>Employee ID</t>
-  </si>
-  <si>
-    <t>Date of joining</t>
-  </si>
-  <si>
-    <t>Probation End Date</t>
-  </si>
-  <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Qualification Degree</t>
-  </si>
-  <si>
-    <t>Work Experience</t>
-  </si>
-  <si>
-    <t>Immediate Manager</t>
-  </si>
-  <si>
-    <t>Immediate Manager Employee Code</t>
-  </si>
-  <si>
-    <t>Leave Approving Authority</t>
-  </si>
-  <si>
-    <t>Leave Approving Authority Employee Code</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Job Role</t>
-  </si>
-  <si>
-    <t>Grade</t>
-  </si>
-  <si>
-    <t>Employement Type</t>
-  </si>
-  <si>
-    <t>Aadhar Number</t>
-  </si>
-  <si>
-    <t>PAN Number</t>
-  </si>
-  <si>
-    <t>Holiday Year</t>
-  </si>
-  <si>
-    <t>Work Pattern</t>
-  </si>
-  <si>
-    <t>Salary</t>
-  </si>
-  <si>
-    <t>Annual Earned Leave Entilement</t>
-  </si>
-  <si>
-    <t>This Year</t>
-  </si>
-  <si>
-    <t>Next Year</t>
+    <t>Rishi</t>
+  </si>
+  <si>
+    <t>Shukla</t>
+  </si>
+  <si>
+    <t>rishi@ncorp.com</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>Web</t>
+  </si>
+  <si>
+    <t>oum</t>
+  </si>
+  <si>
+    <t>weboum@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Singh</t>
+  </si>
+  <si>
+    <t>developer.rahul9888@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-05-13</t>
+  </si>
+  <si>
+    <t>shukla082rishi@gmail.com</t>
+  </si>
+  <si>
+    <t>rishi.shukla.84@gmail.com</t>
+  </si>
+  <si>
+    <t>1986-05-24</t>
+  </si>
+  <si>
+    <t>Ayush</t>
+  </si>
+  <si>
+    <t>mishra</t>
+  </si>
+  <si>
+    <t>mishraji@gmail.com</t>
+  </si>
+  <si>
+    <t>ayush@gmail.com</t>
+  </si>
+  <si>
+    <t>2004-01-01</t>
+  </si>
+  <si>
+    <t>Suraj</t>
+  </si>
+  <si>
+    <t>singh@gmail.com</t>
+  </si>
+  <si>
+    <t>suraj@gmail.com</t>
+  </si>
+  <si>
+    <t>2002-05-10</t>
+  </si>
+  <si>
+    <t>HR web</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>testweb@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-05-01</t>
+  </si>
+  <si>
+    <t>Shubham</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>shubh@gmail.com</t>
+  </si>
+  <si>
+    <t>1995-09-05</t>
+  </si>
+  <si>
+    <t>Shubh</t>
+  </si>
+  <si>
+    <t>S123</t>
+  </si>
+  <si>
+    <t>Shubh123@gmail.com</t>
+  </si>
+  <si>
+    <t>1994-09-06</t>
+  </si>
+  <si>
+    <t>Sourav</t>
+  </si>
+  <si>
+    <t>Thakur</t>
+  </si>
+  <si>
+    <t>test@123.com</t>
+  </si>
+  <si>
+    <t>2024-05-31</t>
+  </si>
+  <si>
+    <t>Kuldeep</t>
+  </si>
+  <si>
+    <t>Chahal</t>
+  </si>
+  <si>
+    <t>test@1234.com</t>
+  </si>
+  <si>
+    <t>2000-02-02</t>
+  </si>
+  <si>
+    <t>Nikhil</t>
+  </si>
+  <si>
+    <t>Saini</t>
+  </si>
+  <si>
+    <t>test1234@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-06-20</t>
+  </si>
+  <si>
+    <t>Rohit</t>
+  </si>
+  <si>
+    <t>Deshmukh</t>
+  </si>
+  <si>
+    <t>test10@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-06-05</t>
+  </si>
+  <si>
+    <t>Karan</t>
+  </si>
+  <si>
+    <t>Rawat</t>
+  </si>
+  <si>
+    <t>test4545@gmail.com</t>
+  </si>
+  <si>
+    <t>Ajay</t>
+  </si>
+  <si>
+    <t>test23@gmail.com</t>
+  </si>
+  <si>
+    <t>abcd@yahoo.com</t>
+  </si>
+  <si>
+    <t>2014-06-09</t>
+  </si>
+  <si>
+    <t>Atul</t>
+  </si>
+  <si>
+    <t>rahuldf@gmail.com</t>
+  </si>
+  <si>
+    <t>2014-06-04</t>
+  </si>
+  <si>
+    <t>Abdul</t>
+  </si>
+  <si>
+    <t>Tkhan</t>
+  </si>
+  <si>
+    <t>rahultest@gmail.com</t>
+  </si>
+  <si>
+    <t>2015-06-10</t>
+  </si>
+  <si>
+    <t>Sunil</t>
+  </si>
+  <si>
+    <t>Kumar</t>
+  </si>
+  <si>
+    <t>testing1231@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-06-02</t>
+  </si>
+  <si>
+    <t>yadav</t>
+  </si>
+  <si>
+    <t>sddkfj@gmail.com</t>
+  </si>
+  <si>
+    <t>2015-06-01</t>
+  </si>
+  <si>
+    <t>Nayan</t>
+  </si>
+  <si>
+    <t>Ganguly</t>
+  </si>
+  <si>
+    <t>jwrgl@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>Banerjee</t>
+  </si>
+  <si>
+    <t>wrg@gmail.com</t>
+  </si>
+  <si>
+    <t>Rachin</t>
+  </si>
+  <si>
+    <t>Ahmed</t>
+  </si>
+  <si>
+    <t>test@gmail.com</t>
+  </si>
+  <si>
+    <t>vaibhav</t>
+  </si>
+  <si>
+    <t>kumar</t>
+  </si>
+  <si>
+    <t>vaibhav34@dfgdf.com</t>
+  </si>
+  <si>
+    <t>2014-06-10</t>
+  </si>
+  <si>
+    <t>testleave</t>
+  </si>
+  <si>
+    <t>testtest@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-06-14</t>
+  </si>
+  <si>
+    <t>shubham</t>
+  </si>
+  <si>
+    <t>st@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-06-15</t>
+  </si>
+  <si>
+    <t>s@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-06-21</t>
+  </si>
+  <si>
+    <t>test emp</t>
+  </si>
+  <si>
+    <t>test emp last</t>
+  </si>
+  <si>
+    <t>testemp@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>onboard</t>
+  </si>
+  <si>
+    <t>onboar last</t>
+  </si>
+  <si>
+    <t>onboar@gmail.com</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Retest</t>
+  </si>
+  <si>
+    <t>User151</t>
+  </si>
+  <si>
+    <t>ru@gmail.com</t>
+  </si>
+  <si>
+    <t>0001-12-05</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>tu@gmail.com</t>
+  </si>
+  <si>
+    <t>0001-06-21</t>
+  </si>
+  <si>
+    <t>testdfg@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-06-13</t>
+  </si>
+  <si>
+    <t>usernew</t>
+  </si>
+  <si>
+    <t>test141@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-06-07</t>
+  </si>
+  <si>
+    <t>sr@gmail.com</t>
+  </si>
+  <si>
+    <t>devansh</t>
+  </si>
+  <si>
+    <t>devansh@j.com</t>
+  </si>
+  <si>
+    <t>2024-06-27</t>
+  </si>
+  <si>
+    <t>Ranjeet</t>
+  </si>
+  <si>
+    <t>ranjeet@ran.com</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>sj@gmail.com</t>
   </si>
   <si>
     <t>First</t>
   </si>
   <si>
-    <t>Middle</t>
-  </si>
-  <si>
     <t>Last</t>
   </si>
   <si>
-    <t>user@gmail.com</t>
-  </si>
-  <si>
-    <t>user1@gmail.com</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>10-07-1995</t>
-  </si>
-  <si>
-    <t>Address 1</t>
-  </si>
-  <si>
-    <t>Address 2</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>01-01-2024</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>Regular</t>
-  </si>
-  <si>
-    <t>2024-2025</t>
-  </si>
-  <si>
-    <t>Full Time</t>
+    <t>use75754546r@gmail.com</t>
+  </si>
+  <si>
+    <t>Arsh</t>
+  </si>
+  <si>
+    <t>Mehta</t>
+  </si>
+  <si>
+    <t>arsh@gmail.com</t>
+  </si>
+  <si>
+    <t>1995-07-10</t>
+  </si>
+  <si>
+    <t>Aditya</t>
+  </si>
+  <si>
+    <t>aditya@yahoo.co.in</t>
+  </si>
+  <si>
+    <t>fjgklfjhkl@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>dhrj</t>
+  </si>
+  <si>
+    <t>rjyrj</t>
+  </si>
+  <si>
+    <t>ehtejnr@gmail.com</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
   </si>
 </sst>
 </file>
@@ -540,10 +795,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AS2"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:45">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -568,220 +823,846 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="E2">
+        <v>9876543212</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="E3">
+        <v>9998887776</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="E4">
+        <v>1234567894</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="E5">
+        <v>9336624642</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="D6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="E6">
+        <v>8765465636</v>
+      </c>
+      <c r="F6">
+        <v>9528748159</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="D7" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="E7">
+        <v>9845186284</v>
+      </c>
+      <c r="F7">
+        <v>9528748159</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="B8" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="C8" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="E8">
+        <v>1212121218</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="B9" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="E9">
+        <v>7389073890</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="B10" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="C10" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="E10">
+        <v>7894561230</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:45">
-      <c r="A2" t="s">
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
         <v>45</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B11" t="s">
         <v>46</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C11" t="s">
         <v>47</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E11">
+        <v>9828900290</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" t="s">
         <v>48</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
         <v>49</v>
       </c>
-      <c r="F2">
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12">
+        <v>8888888888</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13">
+        <v>1234567890</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14">
         <v>1234567894</v>
       </c>
-      <c r="G2">
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15">
+        <v>1234567894</v>
+      </c>
+      <c r="G15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16">
+        <v>9876543212</v>
+      </c>
+      <c r="F16">
+        <v>6565657894</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17">
+        <v>7894561234</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18">
+        <v>4567894564</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19">
+        <v>9876543213</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20">
+        <v>7894561234</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21">
+        <v>7412589635</v>
+      </c>
+      <c r="G21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22">
+        <v>7894561234</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23">
+        <v>9826098260</v>
+      </c>
+      <c r="G23" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24">
+        <v>1212121212</v>
+      </c>
+      <c r="G24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25">
+        <v>123</v>
+      </c>
+      <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25">
+        <v>7389012345</v>
+      </c>
+      <c r="G25" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26">
+        <v>1234567890</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27">
+        <v>123</v>
+      </c>
+      <c r="C27" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27">
+        <v>9898989898</v>
+      </c>
+      <c r="G27" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28">
+        <v>1212121212</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29">
+        <v>1212121212</v>
+      </c>
+      <c r="G29" t="s">
+        <v>110</v>
+      </c>
+      <c r="H29" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" t="s">
+        <v>112</v>
+      </c>
+      <c r="C30" t="s">
+        <v>113</v>
+      </c>
+      <c r="E30">
+        <v>7389073888</v>
+      </c>
+      <c r="G30" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31">
+        <v>7897897890</v>
+      </c>
+      <c r="F31">
+        <v>1234567890</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32">
+        <v>7894561234</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" t="s">
+        <v>122</v>
+      </c>
+      <c r="E33">
+        <v>1212121213</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34">
+        <v>9898989890</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35">
+        <v>8171574791</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" t="s">
+        <v>129</v>
+      </c>
+      <c r="E36">
+        <v>1212122222</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37">
+        <v>7389070888</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" t="s">
+        <v>134</v>
+      </c>
+      <c r="E38">
+        <v>1234567900</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39">
+        <v>8054988585</v>
+      </c>
+      <c r="G39" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>139</v>
+      </c>
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40">
+        <v>9887480543</v>
+      </c>
+      <c r="G40" t="s">
+        <v>110</v>
+      </c>
+      <c r="H40" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41">
         <v>7894561235</v>
       </c>
-      <c r="H2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2">
-        <v>123456</v>
-      </c>
-      <c r="K2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O2" t="s">
-        <v>56</v>
-      </c>
-      <c r="P2">
-        <v>123456</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R2" t="s">
-        <v>53</v>
-      </c>
-      <c r="S2" t="s">
-        <v>54</v>
-      </c>
-      <c r="T2" t="s">
-        <v>55</v>
-      </c>
-      <c r="U2" t="s">
-        <v>56</v>
-      </c>
-      <c r="V2">
-        <v>123456</v>
-      </c>
-      <c r="X2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
+      <c r="G41" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>143</v>
+      </c>
+      <c r="B42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C42" t="s">
+        <v>145</v>
+      </c>
+      <c r="E42">
+        <v>7412587894</v>
+      </c>
+      <c r="G42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/public/uploads/users.xlsx
+++ b/public/uploads/users.xlsx
@@ -119,7 +119,7 @@
     <t>Department</t>
   </si>
   <si>
-    <t>Job Role</t>
+    <t>Designation</t>
   </si>
   <si>
     <t>Grade</t>

--- a/public/uploads/users.xlsx
+++ b/public/uploads/users.xlsx
@@ -194,7 +194,7 @@
     <t>UP</t>
   </si>
   <si>
-    <t>22-07-2024</t>
+    <t>23-07-2024</t>
   </si>
   <si>
     <t>Employee</t>
